--- a/products/Hiring_Job_Posting_AI_Kit_v0.1.xlsx
+++ b/products/Hiring_Job_Posting_AI_Kit_v0.1.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="R3fc2caf89eef445a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Role Intake" sheetId="2" r:id="R2555f9ee41074f39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Job Clarity Builder" sheetId="3" r:id="R699743d03b9a4336"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hiring Risk Check" sheetId="4" r:id="R4488574fe8a74aef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screening Questions" sheetId="5" r:id="Rb3fbb9ab44de479d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate Reply Builder" sheetId="6" r:id="R21aa18e1e5254410"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Posting Tests" sheetId="7" r:id="Ra3b68f72de934d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Pack" sheetId="8" r:id="R6fa1b9397beb4aa7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="はじめに" sheetId="1" r:id="R40e32cb458074eed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職種情報入力" sheetId="2" r:id="Ref30fd13187a441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="求人具体化" sheetId="3" r:id="Rc1ab432e87014f15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="採用表現チェック" sheetId="4" r:id="Rbf7f662cefa74641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事前質問" sheetId="5" r:id="Ra00e6fdcc3f64b1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候補者返信" sheetId="6" r:id="R436eb88faf8a4be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掲載テスト" sheetId="7" r:id="Re21d9c1ab0ba440a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロンプト集" sheetId="8" r:id="R1281bfaefa734ecf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,51 +250,58 @@
       </x:c>
       <x:c r="B1" s="7"/>
     </x:row>
-    <x:row r="2" ht="33" customHeight="1"/>
+    <x:row r="2" ht="33" customHeight="1">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+    </x:row>
     <x:row r="3" ht="33" customHeight="1">
       <x:c r="A3" s="5" t="str">
         <x:v>AIで求人票を書く前に、仕事内容、条件、向いている人、向いていない人、候補者への返信、表現リスクを整理するためのテンプレートです。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="33" customHeight="1"/>
+      <x:c r="B3"/>
+    </x:row>
+    <x:row r="4" ht="33" customHeight="1">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+    </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
-        <x:v>Step 1</x:v>
+        <x:v>手順 1</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Role Intakeに職種、業務、条件、期待成果を入力</x:v>
+        <x:v>職種情報入力に職種、業務、条件、期待成果を入力</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>Step 2</x:v>
+        <x:v>手順 2</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>Job Clarity Builderで曖昧な仕事内容を具体化</x:v>
+        <x:v>求人 明確化 作成で曖昧な仕事内容を具体化</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>Step 3</x:v>
+        <x:v>手順 3</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>Hiring Risk Checkで盛りすぎや不適切表現を削る</x:v>
+        <x:v>採用表現チェックで盛りすぎや不適切表現を削る</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
-        <x:v>Step 4</x:v>
+        <x:v>手順 4</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>Screening Questionsで面接前の確認事項を作る</x:v>
+        <x:v>事前質問で面接前の確認事項を作る</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
-        <x:v>Step 5</x:v>
+        <x:v>手順 5</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>Posting Testsで求人票の改善履歴を記録する</x:v>
+        <x:v>掲載 テストで求人票の改善履歴を記録する</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
@@ -339,482 +346,482 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Field</x:v>
+        <x:v>項目</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Value</x:v>
+        <x:v>入力欄</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Required</x:v>
+        <x:v>必須</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Example</x:v>
+        <x:v>例</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>AI Can Draft?</x:v>
+        <x:v>AIが下書き可?</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Human Must Verify?</x:v>
+        <x:v>人の確認必須?</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Risk If Wrong</x:v>
+        <x:v>間違えた時のリスク</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Use In Posting</x:v>
+        <x:v>求人票で使う範囲</x:v>
       </x:c>
       <x:c r="I1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>職種名</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str"/>
+      <x:c r="B2" s="6"/>
       <x:c r="C2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
         <x:v>店舗スタッフ / Webデザイナー</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
         <x:v>応募ズレ</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Title</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="str"/>
+        <x:v>タイトル</x:v>
+      </x:c>
+      <x:c r="I2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>雇用形態</x:v>
       </x:c>
-      <x:c r="B3" s="6" t="str"/>
+      <x:c r="B3" s="6"/>
       <x:c r="C3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
         <x:v>正社員 / 業務委託 / アルバイト</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
         <x:v>法務/労務リスク</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str">
-        <x:v>Conditions</x:v>
-      </x:c>
-      <x:c r="I3" s="6" t="str"/>
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="I3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>給与/報酬</x:v>
       </x:c>
-      <x:c r="B4" s="6" t="str"/>
+      <x:c r="B4" s="6"/>
       <x:c r="C4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
         <x:v>時給1,300円から</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
         <x:v>トラブル</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
-        <x:v>Conditions</x:v>
-      </x:c>
-      <x:c r="I4" s="6" t="str"/>
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="I4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>勤務地/リモート</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="str"/>
+      <x:c r="B5" s="6"/>
       <x:c r="C5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>東京都 / 一部リモート</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
         <x:v>応募ミスマッチ</x:v>
       </x:c>
       <x:c r="H5" s="6" t="str">
-        <x:v>Conditions</x:v>
-      </x:c>
-      <x:c r="I5" s="6" t="str"/>
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="I5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>勤務時間</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str"/>
+      <x:c r="B6" s="6"/>
       <x:c r="C6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>週3日、10:00-16:00</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
         <x:v>労務リスク</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
-        <x:v>Conditions</x:v>
-      </x:c>
-      <x:c r="I6" s="6" t="str"/>
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="I6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>主な業務</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="str"/>
+      <x:c r="B7" s="6"/>
       <x:c r="C7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
         <x:v>接客、在庫管理、SNS更新</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
         <x:v>期待ズレ</x:v>
       </x:c>
       <x:c r="H7" s="6" t="str">
-        <x:v>Body</x:v>
-      </x:c>
-      <x:c r="I7" s="6" t="str"/>
+        <x:v>本文</x:v>
+      </x:c>
+      <x:c r="I7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>成果物/目標</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="str"/>
+      <x:c r="B8" s="6"/>
       <x:c r="C8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
         <x:v>問い合わせ返信を当日中に対応</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
         <x:v>評価ズレ</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>Body</x:v>
-      </x:c>
-      <x:c r="I8" s="6" t="str"/>
+        <x:v>本文</x:v>
+      </x:c>
+      <x:c r="I8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>必須条件</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="str"/>
+      <x:c r="B9" s="6"/>
       <x:c r="C9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
         <x:v>土日どちらか勤務可能</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
         <x:v>不適切選考</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
-        <x:v>Requirements</x:v>
-      </x:c>
-      <x:c r="I9" s="6" t="str"/>
+        <x:v>要件</x:v>
+      </x:c>
+      <x:c r="I9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>歓迎条件</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="str"/>
+      <x:c r="B10" s="6"/>
       <x:c r="C10" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>Canva経験</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
         <x:v>条件盛りすぎ</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>Nice to have</x:v>
-      </x:c>
-      <x:c r="I10" s="6" t="str"/>
+        <x:v>あるとよい条件</x:v>
+      </x:c>
+      <x:c r="I10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>使うツール</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="str"/>
+      <x:c r="B11" s="6"/>
       <x:c r="C11" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>Google Sheets、Slack</x:v>
+        <x:v>Googleスプレッドシート、Slack</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
         <x:v>入社後ギャップ</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>Body</x:v>
-      </x:c>
-      <x:c r="I11" s="6" t="str"/>
+        <x:v>本文</x:v>
+      </x:c>
+      <x:c r="I11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>向いている人</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="str"/>
+      <x:c r="B12" s="6"/>
       <x:c r="C12" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>丁寧に確認できる人</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
         <x:v>曖昧</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
-        <x:v>Fit</x:v>
-      </x:c>
-      <x:c r="I12" s="6" t="str"/>
+        <x:v>相性</x:v>
+      </x:c>
+      <x:c r="I12" s="6"/>
     </x:row>
     <x:row r="13" ht="33" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>向いていない人</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="str"/>
+      <x:c r="B13" s="6"/>
       <x:c r="C13" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
         <x:v>確認なしに進めたい人</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
         <x:v>強すぎる表現</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>Fit</x:v>
-      </x:c>
-      <x:c r="I13" s="6" t="str"/>
+        <x:v>相性</x:v>
+      </x:c>
+      <x:c r="I13" s="6"/>
     </x:row>
     <x:row r="14" ht="33" hidden="0" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>選考フロー</x:v>
       </x:c>
-      <x:c r="B14" s="6" t="str"/>
+      <x:c r="B14" s="6"/>
       <x:c r="C14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
         <x:v>書類、面談1回</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
         <x:v>離脱</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
-        <x:v>Flow</x:v>
-      </x:c>
-      <x:c r="I14" s="6" t="str"/>
+        <x:v>導線</x:v>
+      </x:c>
+      <x:c r="I14" s="6"/>
     </x:row>
     <x:row r="15" ht="33" hidden="0" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>応募時に欲しい情報</x:v>
       </x:c>
-      <x:c r="B15" s="6" t="str"/>
+      <x:c r="B15" s="6"/>
       <x:c r="C15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
         <x:v>職歴、勤務可能日</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
         <x:v>確認漏れ</x:v>
       </x:c>
       <x:c r="H15" s="6" t="str">
-        <x:v>CTA</x:v>
-      </x:c>
-      <x:c r="I15" s="6" t="str"/>
+        <x:v>行動導線</x:v>
+      </x:c>
+      <x:c r="I15" s="6"/>
     </x:row>
     <x:row r="16" ht="33" hidden="0" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>魅力</x:v>
       </x:c>
-      <x:c r="B16" s="6" t="str"/>
+      <x:c r="B16" s="6"/>
       <x:c r="C16" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
         <x:v>少人数で改善しやすい</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F16" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
         <x:v>誇張</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
-        <x:v>Body</x:v>
-      </x:c>
-      <x:c r="I16" s="6" t="str"/>
+        <x:v>本文</x:v>
+      </x:c>
+      <x:c r="I16" s="6"/>
     </x:row>
     <x:row r="17" ht="33" hidden="0" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>大変な点</x:v>
       </x:c>
-      <x:c r="B17" s="6" t="str"/>
+      <x:c r="B17" s="6"/>
       <x:c r="C17" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
         <x:v>繁忙時間は複数対応</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
         <x:v>早期離職</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
-        <x:v>Body</x:v>
-      </x:c>
-      <x:c r="I17" s="6" t="str"/>
+        <x:v>本文</x:v>
+      </x:c>
+      <x:c r="I17" s="6"/>
     </x:row>
     <x:row r="18" ht="33" hidden="0" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>法令/社内確認</x:v>
       </x:c>
-      <x:c r="B18" s="6" t="str"/>
+      <x:c r="B18" s="6"/>
       <x:c r="C18" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
         <x:v>給与、休日、契約条件</x:v>
       </x:c>
       <x:c r="E18" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F18" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="H18" s="6" t="str">
-        <x:v>Before publish</x:v>
-      </x:c>
-      <x:c r="I18" s="6" t="str"/>
+        <x:v>公開前</x:v>
+      </x:c>
+      <x:c r="I18" s="6"/>
     </x:row>
     <x:row r="19" ht="33" hidden="0" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>公開先</x:v>
       </x:c>
-      <x:c r="B19" s="6" t="str"/>
+      <x:c r="B19" s="6"/>
       <x:c r="C19" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D19" s="6" t="str">
         <x:v>Indeed / Wantedly / X</x:v>
       </x:c>
       <x:c r="E19" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="F19" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
         <x:v>媒体ミス</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
-        <x:v>Distribution</x:v>
-      </x:c>
-      <x:c r="I19" s="6" t="str"/>
+        <x:v>掲載先</x:v>
+      </x:c>
+      <x:c r="I19" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -836,25 +843,25 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Vague Phrase</x:v>
+        <x:v>曖昧な表現</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Problem</x:v>
+        <x:v>問題</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Clarifying Question</x:v>
+        <x:v>確認質問</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Better Phrase</x:v>
+        <x:v>改善表現</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Evidence Needed</x:v>
+        <x:v>必要な根拠</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Use In</x:v>
+        <x:v>使う範囲</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Example</x:v>
+        <x:v>例</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -874,9 +881,9 @@
         <x:v>具体行動</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Fit</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str"/>
+        <x:v>相性</x:v>
+      </x:c>
+      <x:c r="G2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -895,9 +902,9 @@
         <x:v>人数/体制</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Culture</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="str"/>
+        <x:v>職場雰囲気</x:v>
+      </x:c>
+      <x:c r="G3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -916,9 +923,9 @@
         <x:v>業務一覧</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Body</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="str"/>
+        <x:v>本文</x:v>
+      </x:c>
+      <x:c r="G4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -937,9 +944,9 @@
         <x:v>教育内容</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>Appeal</x:v>
-      </x:c>
-      <x:c r="G5" s="6" t="str"/>
+        <x:v>魅力</x:v>
+      </x:c>
+      <x:c r="G5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -958,9 +965,9 @@
         <x:v>手当条件</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>Conditions</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="str"/>
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="G6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -979,9 +986,9 @@
         <x:v>シフト条件</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Conditions</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="str"/>
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="G7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -1000,9 +1007,9 @@
         <x:v>経験年数</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>Requirements</x:v>
-      </x:c>
-      <x:c r="G8" s="6" t="str"/>
+        <x:v>要件</x:v>
+      </x:c>
+      <x:c r="G8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -1021,9 +1028,9 @@
         <x:v>業務要件</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Requirements</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="str"/>
+        <x:v>要件</x:v>
+      </x:c>
+      <x:c r="G9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -1042,9 +1049,9 @@
         <x:v>業務要件</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>Culture</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="str"/>
+        <x:v>職場雰囲気</x:v>
+      </x:c>
+      <x:c r="G10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -1063,9 +1070,9 @@
         <x:v>教育体制</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>Body</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="str"/>
+        <x:v>本文</x:v>
+      </x:c>
+      <x:c r="G11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -1084,9 +1091,9 @@
         <x:v>実績</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>Conditions</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="str"/>
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="G12" s="6"/>
     </x:row>
     <x:row r="13" ht="33" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -1105,9 +1112,9 @@
         <x:v>権限</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>Appeal</x:v>
-      </x:c>
-      <x:c r="G13" s="6" t="str"/>
+        <x:v>魅力</x:v>
+      </x:c>
+      <x:c r="G13" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1129,25 +1136,25 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Risk</x:v>
+        <x:v>リスク</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Why</x:v>
+        <x:v>理由</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Bad Example</x:v>
+        <x:v>悪い例</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Safer Direction</x:v>
+        <x:v>安全な方向</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Severity</x:v>
+        <x:v>重要度</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1167,9 +1174,9 @@
         <x:v>法令確認</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -1188,9 +1195,9 @@
         <x:v>法令確認</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1209,9 +1216,9 @@
         <x:v>給与確認</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -1230,9 +1237,9 @@
         <x:v>労務確認</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G5" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -1251,9 +1258,9 @@
         <x:v>契約確認</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -1272,9 +1279,9 @@
         <x:v>実態確認</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="str"/>
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="G7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -1293,9 +1300,9 @@
         <x:v>教育確認</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G8" s="6" t="str"/>
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="G8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -1314,9 +1321,9 @@
         <x:v>トーン確認</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="str"/>
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="G9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -1335,9 +1342,9 @@
         <x:v>条件確認</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="str"/>
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="G10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -1356,9 +1363,9 @@
         <x:v>運用確認</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="str"/>
+        <x:v>低</x:v>
+      </x:c>
+      <x:c r="G11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -1377,9 +1384,9 @@
         <x:v>媒体確認</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="str"/>
+        <x:v>低</x:v>
+      </x:c>
+      <x:c r="G12" s="6"/>
     </x:row>
     <x:row r="13" ht="33" hidden="0" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -1398,9 +1405,9 @@
         <x:v>実態確認</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="G13" s="6" t="str"/>
+        <x:v>低</x:v>
+      </x:c>
+      <x:c r="G13" s="6"/>
     </x:row>
     <x:row r="14" ht="33" hidden="0" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -1419,9 +1426,9 @@
         <x:v>現場確認</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="G14" s="6" t="str"/>
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="G14" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1443,25 +1450,25 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Question</x:v>
+        <x:v>質問</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Checks</x:v>
+        <x:v>見る点</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Good Signal</x:v>
+        <x:v>よい兆候</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Concern Signal</x:v>
+        <x:v>懸念兆候</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Ask Before Interview?</x:v>
+        <x:v>面接前に聞く?</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Do Not Ask</x:v>
+        <x:v>聞かないこと</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1478,12 +1485,12 @@
         <x:v>抽象的</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
         <x:v>家庭状況</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="str"/>
+      <x:c r="G2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -1499,12 +1506,12 @@
         <x:v>曖昧</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
         <x:v>不必要な個人事情</x:v>
       </x:c>
-      <x:c r="G3" s="6" t="str"/>
+      <x:c r="G3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1520,12 +1527,12 @@
         <x:v>勢いだけ</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
         <x:v>性格断定</x:v>
       </x:c>
-      <x:c r="G4" s="6" t="str"/>
+      <x:c r="G4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -1541,12 +1548,12 @@
         <x:v>全部できます</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
         <x:v>健康情報の深掘り</x:v>
       </x:c>
-      <x:c r="G5" s="6" t="str"/>
+      <x:c r="G5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -1562,12 +1569,12 @@
         <x:v>不明</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
         <x:v>私用アカウント要求</x:v>
       </x:c>
-      <x:c r="G6" s="6" t="str"/>
+      <x:c r="G6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -1583,12 +1590,12 @@
         <x:v>抱え込む</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
         <x:v>圧迫</x:v>
       </x:c>
-      <x:c r="G7" s="6" t="str"/>
+      <x:c r="G7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -1604,12 +1611,12 @@
         <x:v>読んでいない</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
         <x:v>誘導しすぎ</x:v>
       </x:c>
-      <x:c r="G8" s="6" t="str"/>
+      <x:c r="G8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -1625,12 +1632,12 @@
         <x:v>条件だけ</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
         <x:v>価値観の押し付け</x:v>
       </x:c>
-      <x:c r="G9" s="6" t="str"/>
+      <x:c r="G9" s="6"/>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -1646,12 +1653,12 @@
         <x:v>見ていない</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
         <x:v>脅し</x:v>
       </x:c>
-      <x:c r="G10" s="6" t="str"/>
+      <x:c r="G10" s="6"/>
     </x:row>
     <x:row r="11" ht="33" hidden="0" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -1667,12 +1674,12 @@
         <x:v>不明</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
         <x:v>退職理由深掘り</x:v>
       </x:c>
-      <x:c r="G11" s="6" t="str"/>
+      <x:c r="G11" s="6"/>
     </x:row>
     <x:row r="12" ht="33" hidden="0" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -1688,12 +1695,12 @@
         <x:v>なしでも可</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
         <x:v>センシティブ情報要求</x:v>
       </x:c>
-      <x:c r="G12" s="6" t="str"/>
+      <x:c r="G12" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1714,22 +1721,22 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Message Type</x:v>
+        <x:v>メッセージ種別</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Use When</x:v>
+        <x:v>使う場面</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Structure</x:v>
+        <x:v>構成</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Include</x:v>
+        <x:v>入れること</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Avoid</x:v>
+        <x:v>避けること</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Example CTA</x:v>
+        <x:v>例 CTA</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1933,125 +1940,125 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Date</x:v>
+        <x:v>日付</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Change</x:v>
+        <x:v>変更内容</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Before Views</x:v>
+        <x:v>変更前閲覧</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>After Views</x:v>
+        <x:v>変更後閲覧</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Applications</x:v>
+        <x:v>応募数</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Qualified</x:v>
+        <x:v>有望数</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Objection</x:v>
+        <x:v>反応・懸念</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Learning</x:v>
+        <x:v>学び</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
-      <x:c r="A2" s="6" t="str"/>
+      <x:c r="A2" s="6"/>
       <x:c r="B2" s="6" t="str">
         <x:v>職種名を具体化</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str"/>
-      <x:c r="D2" s="6" t="str"/>
-      <x:c r="E2" s="6" t="str"/>
-      <x:c r="F2" s="6" t="str"/>
-      <x:c r="G2" s="6" t="str"/>
-      <x:c r="H2" s="6" t="str"/>
+      <x:c r="C2" s="6"/>
+      <x:c r="D2" s="6"/>
+      <x:c r="E2" s="6"/>
+      <x:c r="F2" s="6"/>
+      <x:c r="G2" s="6"/>
+      <x:c r="H2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
-      <x:c r="A3" s="6" t="str"/>
+      <x:c r="A3" s="6"/>
       <x:c r="B3" s="6" t="str">
         <x:v>大変な点を追加</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="str"/>
-      <x:c r="D3" s="6" t="str"/>
-      <x:c r="E3" s="6" t="str"/>
-      <x:c r="F3" s="6" t="str"/>
-      <x:c r="G3" s="6" t="str"/>
-      <x:c r="H3" s="6" t="str"/>
+      <x:c r="C3" s="6"/>
+      <x:c r="D3" s="6"/>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
-      <x:c r="A4" s="6" t="str"/>
+      <x:c r="A4" s="6"/>
       <x:c r="B4" s="6" t="str">
         <x:v>給与条件を明確化</x:v>
       </x:c>
-      <x:c r="C4" s="6" t="str"/>
-      <x:c r="D4" s="6" t="str"/>
-      <x:c r="E4" s="6" t="str"/>
-      <x:c r="F4" s="6" t="str"/>
-      <x:c r="G4" s="6" t="str"/>
-      <x:c r="H4" s="6" t="str"/>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="6"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
-      <x:c r="A5" s="6" t="str"/>
+      <x:c r="A5" s="6"/>
       <x:c r="B5" s="6" t="str">
         <x:v>向いている人を具体化</x:v>
       </x:c>
-      <x:c r="C5" s="6" t="str"/>
-      <x:c r="D5" s="6" t="str"/>
-      <x:c r="E5" s="6" t="str"/>
-      <x:c r="F5" s="6" t="str"/>
-      <x:c r="G5" s="6" t="str"/>
-      <x:c r="H5" s="6" t="str"/>
+      <x:c r="C5" s="6"/>
+      <x:c r="D5" s="6"/>
+      <x:c r="E5" s="6"/>
+      <x:c r="F5" s="6"/>
+      <x:c r="G5" s="6"/>
+      <x:c r="H5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
-      <x:c r="A6" s="6" t="str"/>
+      <x:c r="A6" s="6"/>
       <x:c r="B6" s="6" t="str">
         <x:v>応募CTAを変更</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str"/>
-      <x:c r="D6" s="6" t="str"/>
-      <x:c r="E6" s="6" t="str"/>
-      <x:c r="F6" s="6" t="str"/>
-      <x:c r="G6" s="6" t="str"/>
-      <x:c r="H6" s="6" t="str"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="6"/>
+      <x:c r="E6" s="6"/>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="6"/>
+      <x:c r="H6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
-      <x:c r="A7" s="6" t="str"/>
+      <x:c r="A7" s="6"/>
       <x:c r="B7" s="6" t="str">
         <x:v>選考フローを追加</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str"/>
-      <x:c r="D7" s="6" t="str"/>
-      <x:c r="E7" s="6" t="str"/>
-      <x:c r="F7" s="6" t="str"/>
-      <x:c r="G7" s="6" t="str"/>
-      <x:c r="H7" s="6" t="str"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6"/>
+      <x:c r="F7" s="6"/>
+      <x:c r="G7" s="6"/>
+      <x:c r="H7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
-      <x:c r="A8" s="6" t="str"/>
+      <x:c r="A8" s="6"/>
       <x:c r="B8" s="6" t="str">
         <x:v>写真/職場説明を追加</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str"/>
-      <x:c r="D8" s="6" t="str"/>
-      <x:c r="E8" s="6" t="str"/>
-      <x:c r="F8" s="6" t="str"/>
-      <x:c r="G8" s="6" t="str"/>
-      <x:c r="H8" s="6" t="str"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6"/>
+      <x:c r="F8" s="6"/>
+      <x:c r="G8" s="6"/>
+      <x:c r="H8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
-      <x:c r="A9" s="6" t="str"/>
+      <x:c r="A9" s="6"/>
       <x:c r="B9" s="6" t="str">
         <x:v>媒体を変更</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str"/>
-      <x:c r="D9" s="6" t="str"/>
-      <x:c r="E9" s="6" t="str"/>
-      <x:c r="F9" s="6" t="str"/>
-      <x:c r="G9" s="6" t="str"/>
-      <x:c r="H9" s="6" t="str"/>
+      <x:c r="C9" s="6"/>
+      <x:c r="D9" s="6"/>
+      <x:c r="E9" s="6"/>
+      <x:c r="F9" s="6"/>
+      <x:c r="G9" s="6"/>
+      <x:c r="H9" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2070,16 +2077,16 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Prompt</x:v>
+        <x:v>プロンプト</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Use</x:v>
+        <x:v>用途</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Text</x:v>
+        <x:v>本文</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
